--- a/results/bloc logement.xlsx
+++ b/results/bloc logement.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>Payback_REHAB_CB  = ( UC_K_REHAB_CB  * BUIL_D_CB  - UC_K_CB  * BUIL_D_CB )  / ( UC_E_CB  - UC_E_REHAB_CB )  - 1</t>
   </si>
@@ -45,6 +45,18 @@
   </si>
   <si>
     <t>-14.82631310262216</t>
+  </si>
+  <si>
+    <t>V2</t>
+  </si>
+  <si>
+    <t>d(tau_REHAB_N_H01_CB)  = ( @year &gt; 2006 )  * (  - nu_REHAB_H01_CB  * dlog(Payback_REHAB_H01_CB) )</t>
+  </si>
+  <si>
+    <t>0.066</t>
+  </si>
+  <si>
+    <t>nu_rehab</t>
   </si>
 </sst>
 </file>
@@ -80,9 +92,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -363,18 +376,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="11.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>2030</v>
       </c>
@@ -397,23 +410,23 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="C5">
         <f>(C2*H2-D2*H2)/(E2-F2)-1</f>
         <v>-0.9999682727498046</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
         <v>3</v>
       </c>
@@ -421,12 +434,51 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
         <v>5</v>
       </c>
       <c r="C8" t="s">
         <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="L9">
+        <f>37/2.54</f>
+        <v>14.566929133858267</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="2">
+        <v>1.3632281499999999E-5</v>
+      </c>
+      <c r="D11" s="2">
+        <v>1.00353452E-7</v>
+      </c>
+      <c r="E11" s="2">
+        <v>4.8499413100000001E-6</v>
+      </c>
+      <c r="F11" s="2">
+        <v>2.38438337E-6</v>
+      </c>
+      <c r="H11" s="2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
